--- a/data/trans_orig/IP31KM02_R_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM02_R_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37130</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31388</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>69,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>34767</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22715</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42137</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39128</t>
+          <t>31764</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31788</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44929</t>
+          <t>36621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>73895</t>
+          <t>68894</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59580</t>
+          <t>60815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>76535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16585</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10871</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22327</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,88%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>18932</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11562</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30984</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>35,26%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>57,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>14141</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26557</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>30726</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28172</t>
+          <t>23085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52463</t>
+          <t>38805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>312675</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>291968</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>331239</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>400</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>272570</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>221649</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>296448</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>60,33%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>65,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>336473</t>
+          <t>271868</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>312647</t>
+          <t>252646</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>357598</t>
+          <t>286691</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>609043</t>
+          <t>584544</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>541331</t>
+          <t>556460</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>639984</t>
+          <t>612242</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>153748</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>135184</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>174455</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>179262</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>155384</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>230183</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>39,67%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>50,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>168777</t>
+          <t>152798</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147652</t>
+          <t>137975</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>192603</t>
+          <t>172020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>348039</t>
+          <t>306546</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>317098</t>
+          <t>278848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>415751</t>
+          <t>334630</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>109197</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>98157</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>119349</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>95262</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>85383</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>103743</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>65,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>58,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>70,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>116886</t>
+          <t>97064</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103864</t>
+          <t>86989</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128143</t>
+          <t>106551</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>212148</t>
+          <t>206261</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197372</t>
+          <t>192947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>227614</t>
+          <t>221028</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57489</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47337</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>68529</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>50924</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>42443</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>60803</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>34,83%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64253</t>
+          <t>50076</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52996</t>
+          <t>40589</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77275</t>
+          <t>60151</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>115176</t>
+          <t>107564</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99710</t>
+          <t>92797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129952</t>
+          <t>120878</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,52%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>459003</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>435647</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>481165</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>66,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>63,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70,06%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>593</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>402600</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>350163</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>432082</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>61,78%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>53,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>66,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>492487</t>
+          <t>400696</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>462686</t>
+          <t>382002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>516775</t>
+          <t>421549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>895087</t>
+          <t>859699</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>839121</t>
+          <t>827558</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>934456</t>
+          <t>890571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>227821</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>205659</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>251177</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>33,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>36,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>249117</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>219635</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>301554</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38,22%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>46,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>252246</t>
+          <t>217015</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>227958</t>
+          <t>196162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>282047</t>
+          <t>235709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>501363</t>
+          <t>444836</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>461994</t>
+          <t>413964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>557329</t>
+          <t>476977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
